--- a/client-docs/test-cases/emg-o-test-cases-day-in-life.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-day-in-life.xlsx
@@ -2381,29 +2381,32 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>กด "Create Cut Order" จากฟอร์ม Block ที่มีต้นทุนจริงแล้ว</t>
+          <t>สร้าง MO ตัด (Cut-to-Order) เอง จากแอป Manufacturing โดยเลือก Block ที่มีต้นทุนจริงแล้ว</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Block มีต้นทุนจริงจาก PO ตาม TC-D5-01 และมี SO รอตัดอยู่</t>
+          <t>Block มีต้นทุนจริงจาก PO ตาม TC-D5-01, มี SO รอตัดอยู่, และ Block ถูกย้ายไป Location "Stone Production" แล้ว (ทำ Internal Transfer จาก "Stone Available" ก่อน)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดฟอร์ม Block
-2. กดปุ่ม "Create Cut Order"
-3. ระบุขนาดที่จะตัดตาม SO แล้วยืนยัน</t>
+          <t>1. เปิดเมนู Manufacturing &gt; Manufacturing Orders &gt; New
+2. เลือกช่อง "Stone Bundle" เป็น Block นี้ — สังเกต Product/Bill of Materials เติมให้อัตโนมัติ (onchange), Target L/Target H เติมค่าเริ่มต้นจากขนาด Block
+3. เลือกช่อง "Sale Order Line" เป็นบรรทัด SO ที่รอตัด
+4. ปรับ Target L (M) / Target H (M) ตามขนาดที่จะตัดจริง
+5. กด Confirm</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Target L (M) = 2.0
+Target H (M) = 1.2</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Cut Order สร้างสำเร็จ อ้างอิงต้นทุนจริงของ Block นี้ (ไม่ใช่ค่าประเมินตอน Setup) ในการคำนวณต้นทุนแผ่นที่ตัดได้</t>
+          <t>Confirm สำเร็จ (ไม่ถูกบล็อกเพราะ Block อยู่ที่ Stone Production แล้ว) — ต้นทุนวัตถุดิบของ MO อ้างอิงต้นทุนจริงของ Block นี้ (PO Cost + Landed Cost ตาม TC-D5-01/02 ไม่ใช่ค่าประเมินตอน Setup) และปริมาณวัตถุดิบที่ MO จองถูกตั้งเป็น Target CBM จริงตามขนาดที่กรอก (ไม่ใช่ค่า placeholder ของ BOM)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2411,7 +2414,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>⚠️ เอกสารเดิมเขียนตามปุ่ม "Create Cut Order" wizard บนฟอร์ม Block — wizard นั้นถูกรื้อออกแล้ว 13 ก.ย. 2026 พร้อม Factory Worklist page เดิมทั้งหน้า (ADR-061) ตอนนี้ Admin สร้าง Manufacturing Order เองตรงในแอป Manufacturing แทน ไม่มี wizard คั่นกลางอีกต่อไป (ADR-062) — Block ต้องถูกย้ายไป Location "Stone Production" ก่อนเสมอ (Internal Transfer, กฎเดิมจาก ADR-053 ยังใช้อยู่) ไม่เช่นนั้น Confirm จะถูกบล็อก</t>
+        </is>
+      </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
@@ -2525,30 +2532,29 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ยืนยัน Cut Order — แผ่นที่ตัดได้ผูกกับ SO เดิมโดยอัตโนมัติ</t>
+          <t>Mark as Done ให้ MO ตัด — แผ่นที่ตัดได้ผูกกับ SO เดิมโดยอัตโนมัติ</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Cut Order (MO) ผูกกับ Sale Order Line อยู่แล้ว (สร้างจาก TC-D5-04)</t>
+          <t>MO ตัดจาก TC-D5-04 Confirm แล้ว (state=Confirmed) ผูกกับ Sale Order Line เดิม</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. ระบุขนาดที่จะตัด (L × H)
-2. ยืนยัน Cut Order จนเสร็จ
-3. เปิดแผ่นที่ได้ดู Lot/Serial + ลิงก์กลับ SO</t>
+          <t>1. เปิด MO จาก TC-D5-04
+2. กด "Mark as Done" ให้ MO ตัดแผ่นจริง
+3. เปิดแผ่น (Slab) ที่ได้ดู Lot/Serial + ลิงก์กลับ SO</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Slab L (M) = 2.0
-Slab H (M) = 1.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>แผ่นที่ตัดได้ถูก Hold ให้กับ Sale Order Line เดิมทันที พร้อม Lot/Serial เฉพาะแผ่น</t>
+          <t>แผ่นที่ตัดได้ถูก Hold ให้กับ Sale Order Line เดิมทันที พร้อม Lot/Serial เฉพาะแผ่น ขนาดตรงกับ Target L/H ที่กรอกไว้ตอน Confirm</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -2558,7 +2564,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>regression ของ TC-B3 กลุ่ม Cut-to-Order</t>
+          <t>regression ของ TC-B3 กลุ่ม Cut-to-Order — กลไกใหม่ (native MO ไม่มี wizard แล้ว เปลี่ยน 13 ก.ย. 2026 ดู ADR-061/062)</t>
         </is>
       </c>
       <c r="I4" s="7" t="n"/>
@@ -2579,13 +2585,13 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>SO Line ที่ผูก Cut Order นี้มี Analytic Distribution อยู่แล้ว (จาก D2/D3-02)</t>
+          <t>SO Line ที่ผูก MO นี้มี Analytic Distribution อยู่แล้ว (จาก D2/D3-02)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. ยืนยัน Cut Order จนเสร็จ
-2. เปิดรายงาน Analytic Items กรองด้วยชื่อ Cut Order นี้</t>
+          <t>1. ทำตาม TC-D6-01 จนแผ่นถูกตัดจริงแล้ว (MO state=Done)
+2. เปิดรายงาน Analytic Items กรองด้วยชื่อ MO นี้</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2622,13 +2628,13 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>SO Line ที่ผูก Cut Order นี้มี Analytic Distribution ตั้งไว้ 2 Plan พร้อมกัน ("โครงการ" และ "ประเภทวัสดุ")</t>
+          <t>SO Line ที่ผูก MO นี้มี Analytic Distribution ตั้งไว้ 2 Plan พร้อมกัน ("โครงการ" และ "ประเภทวัสดุ")</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. ยืนยัน Cut Order จนเสร็จ (มี Workorder บันทึกเวลาแล้ว)
-2. เปิดรายงาน Analytic Items กรองด้วยชื่อ Cut Order นี้ หารายการ "Stone Cutting Labor"</t>
+          <t>1. ทำตาม TC-D6-01 จนแผ่นถูกตัดจริงแล้ว (มี Workorder บันทึกเวลาแล้ว บน Work Center Gangsaw/Transport)
+2. เปิดรายงาน Analytic Items กรองด้วยชื่อ MO นี้ หารายการ "Stone Cutting Labor"</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2648,7 +2654,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>⚠️ โค้ดจุดนี้เปลี่ยน 2026-08-26 (รองรับหลาย Plan พร้อมกันในบรรทัดเดียว) — วันก่อนทำเอกสารนี้ ยังไม่เคยมี Test Case คุมจุดนี้มาก่อน เสี่ยง regression สูงสุดในหมวดนี้</t>
+          <t>⚠️ โค้ดจุดนี้เปลี่ยน 2026-08-26 (รองรับหลาย Plan พร้อมกันในบรรทัดเดียว) — วันก่อนทำเอกสารนี้ ยังไม่เคยมี Test Case คุมจุดนี้มาก่อน เสี่ยง regression สูงสุดในหมวดนี้ (mechanism เปลี่ยนเป็น native MO 13 ก.ย. 2026 แต่การติดป้าย Analytic ของค่าแรงตัดไม่ได้ถูกแก้ไขในรอบนั้น)</t>
         </is>
       </c>
       <c r="I6" s="7" t="n"/>
@@ -2664,20 +2670,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cut Order แบบไม่มี SO ผูก (ตัดเข้าสต็อกล่วงหน้า) — เลือก Project (No SO)</t>
+          <t>MO ตัดแบบไม่มี SO ผูก (ตัดเข้าสต็อกล่วงหน้า) — กรอก Project (No SO)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Block ยังไม่มี SO ผูก แต่ต้องการตัดเข้าสต็อกไว้ล่วงหน้า</t>
+          <t>Block ยังไม่มี SO ผูก แต่ต้องการตัดเข้าสต็อกไว้ล่วงหน้า — Block อยู่ที่ Stone Production แล้ว</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Cut Order Wizard แบบไม่มี SO
-2. เลือกช่อง "Project (No SO)" เป็น Analytic Account ที่ต้องการ
-3. ยืนยัน Cut Order จนเสร็จ
-4. เปิดรายงาน Analytic Items ดู</t>
+          <t>1. เปิดเมนู Manufacturing &gt; Manufacturing Orders &gt; New เลือกช่อง "Stone Bundle" เป็น Block ที่จะตัด โดยไม่เลือก Sale Order Line
+2. กรอกช่อง "Reason (No SO)"
+3. กรอกช่อง "Project (No SO)" เป็น Analytic Account ที่ต้องการ
+4. กด Confirm แล้ว "Mark as Done" ให้ MO ตัดแผ่นจริง
+5. เปิดรายงาน Analytic Items ดู</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2697,7 +2704,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>ADR-032 regression</t>
+          <t>ADR-032 regression — ⚠️ ไม่มี Cut Order Wizard แล้ว ปรับ step เป็นกรอกช่อง "Reason (No SO)"/"Project (No SO)" ตรงบนฟอร์ม MO เอง (ADR-061/062, ทั้งสองช่องยังอยู่บน mrp.production เดิม)</t>
         </is>
       </c>
       <c r="I7" s="7" t="n"/>
@@ -2713,18 +2720,19 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cut Order ครั้งแรกของบริษัทที่ยังไม่เคยมี Workcenter "Stone Cutting"</t>
+          <t>สร้าง MO ตัดครั้งแรกของ Material+บริษัทคู่ใหม่ที่ยังไม่เคยมี Bill of Materials</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>บริษัทนี้ยังไม่เคยมี mrp.workcenter ชื่อ "Stone Cutting" มาก่อน</t>
+          <t>Material นี้ยังไม่เคยสร้าง MO ตัด (Cut-to-Order) สำหรับบริษัทนี้เลย (ยังไม่มี Bill of Materials ผูกกับ Material+บริษัทนี้)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1. สั่ง Cut Order ครั้งแรกของบริษัทนี้
-2. ตรวจ Manufacturing &gt; Work Centers</t>
+          <t>1. สั่งตัด (สร้าง MO เลือก Stone Bundle, Confirm) ครั้งแรกของ Material/บริษัทนี้ตามขั้นตอน TC-D5-04
+2. ตรวจ Manufacturing &gt; Bill of Materials ของสินค้า Block/Slab นี้
+3. ตรวจ Manufacturing &gt; Work Centers ของบริษัทนี้</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2734,7 +2742,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>ระบบสร้าง Workcenter "Stone Cutting" ให้อัตโนมัติ 1 ตัวต่อบริษัท ไม่ error แม้ยังไม่เคยตั้งมาก่อน</t>
+          <t>ระบบสร้าง Bill of Materials ให้อัตโนมัติ 1 ใบ (routing Transport → Gangsaw) ไม่ error แม้ยังไม่เคยมี BOM มาก่อน — Work Center "Gangsaw"/"Transport" มีอยู่แล้วล่วงหน้าทั้ง 8 ตัวต่อบริษัท (ไม่ได้ถูกสร้างใหม่ตอนนี้)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2744,7 +2752,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>regression เบา ของ TC-A6 กลุ่ม BOM auto-provisioning</t>
+          <t>regression เบา ของ TC-A6 กลุ่ม BOM auto-provisioning — ⚠️ เอกสารเดิมอ้างว่า Workcenter "Stone Cutting" ถูกสร้างอัตโนมัติตอนสั่งตัดครั้งแรก แต่หลัง ADR-062 (13 ก.ย. 2026) work center ทั้ง 8 ตัว (Gangsaw/Transport/...) ถูก provision ไว้ล่วงหน้าต่อบริษัทแล้วเสมอ (ไม่ได้สร้างตอนสั่งตัด) — ตัวที่ยังสร้างอัตโนมัติตอนสั่งตัดครั้งแรกจริงคือ Bill of Materials เท่านั้น ปรับ Test Case ให้ตรงกับกลไกปัจจุบัน</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>
